--- a/fax_checker/Websites.xlsx
+++ b/fax_checker/Websites.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brianethan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F8F1C59-7C2E-413B-989F-75DFEB3B713D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEE566A7-4539-46E2-96D5-41B2E8E34F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E9CD9248-1B12-4629-985D-D5D4ADAE35B3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D358A9B2-32DC-4283-875D-A35C38702111}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,306 +39,1401 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="466">
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Name </t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Street</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Website</t>
+  </si>
+  <si>
+    <t>Addiction treatment center</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/California+Council+of+Community+Behavioral+Health+Agencies/data=!4m7!3m6!1s0x809ad12835867f1b:0x237b27ce0d661f42!8m2!3d38.5793984!4d-121.5021152!16s%2Fg%2F11cm_2bms7!19sChIJG3-GNSjRmoARQh9mDc4neyM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>California Council of Community Behavioral Health Agencies</t>
+  </si>
+  <si>
+    <t>Association / Organization</t>
+  </si>
+  <si>
+    <t>455 Capitol Mall Ste 315</t>
+  </si>
   <si>
     <t>https://www.cccbha.org/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/California+Behavioral+Care,+LLC/data=!4m7!3m6!1s0x80c2c3403521dfe5:0x8ec7f49cd23f2eb8!8m2!3d34.1390506!4d-118.2045012!16s%2Fg%2F11hynfcn57!19sChIJ5d8hNUDDwoARuC4_0pz0x44?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>California Behavioral Care, LLC</t>
+  </si>
+  <si>
+    <t>Mental health service</t>
+  </si>
+  <si>
+    <t>1722 1/2 Colorado Blvd</t>
+  </si>
+  <si>
     <t>http://www.californiabehavioralcare.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Health+For+California+-+Covered+CA+Enrollment/data=!4m7!3m6!1s0x808447f81dcf29bb:0xb47bb6499a55e777!8m2!3d38.4527366!4d-122.6732604!16s%2Fg%2F1q66qmhwb!19sChIJuynPHfhHhIARd-dVmkm2e7Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Health For California - Covered CA Enrollment</t>
+  </si>
+  <si>
+    <t>Health insurance agency</t>
+  </si>
+  <si>
+    <t>4000 Montgomery Dr d7</t>
+  </si>
+  <si>
     <t>https://www.healthforcalifornia.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Fresno+County+Behavioral+Health+-+Managed+Care/data=!4m7!3m6!1s0x80945e5aee3ad5b1:0x28a0b1d5ce1b377b!8m2!3d36.7381786!4d-119.7520603!16s%2Fg%2F11cjk3ty45!19sChIJsdU67lpelIARezcbztWxoCg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Fresno County Behavioral Health - Managed Care</t>
+  </si>
+  <si>
+    <t>4409 E Inyo St building 332</t>
+  </si>
+  <si>
     <t>https://www.fresnocountyca.gov/Departments/Behavioral-Health/Providers/Plan-Administration</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/California+Mental+Health/data=!4m7!3m6!1s0x6ec4eb3f69d77e3:0x1b970055b102b77!8m2!3d37.1135373!4d-121.5965292!16s%2Fg%2F11sw6r59t6!19sChIJ43ed9rNO7AYRdysQWwVwuQE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>California Mental Health</t>
+  </si>
+  <si>
+    <t>14865 Marie Ct</t>
+  </si>
+  <si>
     <t>https://camentalhealth.com/service-area/santa-clara-county/residential-mental-health-clinic-in-san-martin/?utm_campaign=gmb</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/California+Behavioral+Care,+LLC/data=!4m7!3m6!1s0x80c2971f978dcb93:0x11dfd3758c70b48e!8m2!3d34.1637439!4d-118.4491216!16s%2Fg%2F11q_klkxm3!19sChIJk8uNlx-XwoARjrRwjHXT3xE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>5121 Van Nuys Blvd #209</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Southern+California+Behavioral+Health+Group/data=!4m7!3m6!1s0x80c299c266110947:0x2a031f8d5406bef3!8m2!3d34.1688407!4d-118.502034!16s%2Fg%2F11b7q78kby!19sChIJRwkRZsKZwoAR874GVI0fAyo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Southern California Behavioral Health Group</t>
+  </si>
+  <si>
+    <t>Mental health clinic</t>
+  </si>
+  <si>
+    <t>5363 Balboa Blvd #245</t>
+  </si>
+  <si>
     <t>http://www.calabasas-psychiatrist.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/California+Mental+Health/data=!4m7!3m6!1s0x8091dfe472b1e263:0x3bba9ecb08978a9a!8m2!3d37.1078824!4d-121.5850333!16s%2Fg%2F11y7h8dqzc!19sChIJY-KxcuTfkYARmoqXCMueujs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>14210 Lesley Ln</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Community+Behavioral+Health+Center/data=!4m7!3m6!1s0x80945d33af08d913:0xbe934206552ee521!8m2!3d36.8403194!4d-119.7576941!16s%2Fg%2F1yl46r11f!19sChIJE9kIrzNdlIARIeUuVQZCk74?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Community Behavioral Health Center</t>
+  </si>
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>7171 N Cedar Ave</t>
+  </si>
+  <si>
     <t>https://www.communitymedical.org/hospitals-facilities/Community-Behavioral-Health-Center</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Fresno+County+Department+of+Behavioral+Health/data=!4m7!3m6!1s0x80945e2140000001:0x8dd80f0a53e012b0!8m2!3d36.7873185!4d-119.7876789!16s%2Fg%2F1tm8kv5h!19sChIJAQAAQCFelIARsBLgUwoP2I0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Fresno County Department of Behavioral Health</t>
+  </si>
+  <si>
+    <t>1925 E Dakota Ave</t>
+  </si>
+  <si>
     <t>http://www.co.fresno.ca.us/behavioralhealth</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/MHAC+%E2%80%93+Mental+Health+Advisors+%26+Care+California/data=!4m7!3m6!1s0x809443f5940682e3:0xfd3bddb5f57af474!8m2!3d36.8453609!4d-119.7828131!16s%2Fg%2F11myvsqdr8!19sChIJ44IGlPVDlIARdPR69bXdO_0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>MHAC â€“ Mental Health Advisors &amp; Care California</t>
+  </si>
+  <si>
+    <t>Rehabilitation center</t>
+  </si>
+  <si>
+    <t>7462 N Fresno St</t>
+  </si>
+  <si>
     <t>http://mhaccare.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/County+of+orange+health+care+agency+behavioral+health+services/data=!4m7!3m6!1s0x80dcd9eae51c7fa3:0x170255fd925bd767!8m2!3d33.7833733!4d-117.8958645!16s%2Fg%2F11ryqwzv68!19sChIJo38c5erZ3IARZ9dbkv1VAhc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>County of orange health care agency behavioral health services</t>
+  </si>
+  <si>
+    <t>500 City Pkwy W</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Adventist+Health+Behavioral+Health/data=!4m7!3m6!1s0x8094c36de2d331c7:0x64eaec52b5763e40!8m2!3d36.3364863!4d-119.6452531!16s%2Fg%2F11x5gy1wwk!19sChIJxzHT4m3DlIARQD52tVLs6mQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Adventist Health Behavioral Health</t>
+  </si>
+  <si>
+    <t>1025 N Douty St 1st Floor</t>
+  </si>
+  <si>
     <t>https://adventisthealth.org/locations/detail/adventist-health-medical-offices-4324/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/San+Jose+Behavioral+Health/data=!4m7!3m6!1s0x808e2e5093dfa685:0x94e036a5fb81d474!8m2!3d37.2489656!4d-121.7744243!16s%2Fg%2F11ckbtmybj!19sChIJhabfk1AujoARdNSB-6U24JQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>San Jose Behavioral Health</t>
+  </si>
+  <si>
+    <t>455 Silicon Valley Blvd</t>
+  </si>
+  <si>
     <t>https://www.sanjosebh.com/?utm_source=Google&amp;utm_medium=organic&amp;utm_campaign=listing&amp;utm_term=brand</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/San+Joaquin+County+Behavioral+Health+Services/data=!4m7!3m6!1s0x80900d671b0ce66b:0x75e15d635cb684d3!8m2!3d37.9665002!4d-121.2874369!16s%2Fg%2F1tdn4b7w!19sChIJa-YMG2cNkIAR04S2XGNd4XU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>San Joaquin County Behavioral Health Services</t>
+  </si>
+  <si>
+    <t>1212 N California St</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Behavioral+Health+Services+Inc./data=!4m7!3m6!1s0x80dd35cf15340001:0xb701bb4ab4595ecb!8m2!3d33.789916!4d-118.2628721!16s%2Fg%2F11fll61jmp!19sChIJAQA0Fc813YARy15ZtEq7Abc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Behavioral Health Services Inc.</t>
+  </si>
+  <si>
+    <t>1334 N Avalon Blvd</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Doctors+Behavioral+Health+Center/data=!4m7!3m6!1s0x809055c11cedc8ab:0x86c7a47335588c2f!8m2!3d37.6656675!4d-120.9225601!16s%2Fg%2F1tj33cfw!19sChIJq8jtHMFVkIARL4xYNXOkx4Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Doctors Behavioral Health Center</t>
+  </si>
+  <si>
+    <t>1501 Claus Rd</t>
+  </si>
+  <si>
     <t>https://www.cvdoctorshealthsystem.com/locations/detail/doctors-behavioral-health-center</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Clear+Behavioral+Health+-+Virtual+Mental+Health+Services+in+Fresno/data=!4m7!3m6!1s0x809461b2a281b53d:0x508ca866a9b1ac41!8m2!3d36.7378415!4d-119.7950026!16s%2Fg%2F11ymzjf8v2!19sChIJPbWBorJhlIARQayxqWaojFA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Clear Behavioral Health - Virtual Mental Health Services in Fresno</t>
+  </si>
+  <si>
+    <t>1401 Fulton St Ste 914</t>
+  </si>
+  <si>
     <t>https://clearbehavioralhealth.com/locations/virtual-mental-health-services-california/?utm_source=Google&amp;utm_medium=GBP&amp;utm_campaign=Fresno</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Sierra+Meadows+Behavioral+Health/data=!4m7!3m6!1s0x80945d10eb256407:0x8510c33d18a57b83!8m2!3d36.8388329!4d-119.7504579!16s%2Fg%2F11h651mdbn!19sChIJB2Ql6xBdlIARg3ulGD3DEIU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Sierra Meadows Behavioral Health</t>
+  </si>
+  <si>
+    <t>1781 E Fir Ave Ste 102</t>
+  </si>
+  <si>
     <t>https://sierrameadowsbehavioralhealth.com/?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=gbp&amp;utm_content=fresno</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Behavioral+Health+Consultants/data=!4m7!3m6!1s0x80c365c5908098ab:0xcea7cbd6ee9d9594!8m2!3d34.5123592!4d-117.32726!16s%2Fg%2F1ttdyqvh!19sChIJq5iAkMVlw4ARlJWd7tbLp84?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Behavioral Health Consultants</t>
+  </si>
+  <si>
+    <t>15434 W Sage St</t>
+  </si>
+  <si>
     <t>http://www.fbhcinc.net/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Health+Plan+of+San+Mateo/data=!4m7!3m6!1s0x808f78540d4dd873:0x42f4bd80fba21331!8m2!3d37.6605469!4d-122.3984401!16s%2Fg%2F1tglhk4d!19sChIJc9hNDVR4j4ARMROi-4C99EI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Health Plan of San Mateo</t>
+  </si>
+  <si>
+    <t>Non-profit organization</t>
+  </si>
+  <si>
+    <t>801 Gateway Blvd #100</t>
+  </si>
+  <si>
     <t>https://www.hpsm.org/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Oakland+Twenty-First+Street+VA+Clinic/data=!4m7!3m6!1s0x808f80add1ac7c93:0x710bfb9fc03cf020!8m2!3d37.8099933!4d-122.2706355!16s%2Fg%2F1tdjrckj!19sChIJk3ys0a2Aj4ARIPA8wJ_7C3E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Oakland Twenty-First Street VA Clinic</t>
+  </si>
+  <si>
+    <t>Veterans hospital</t>
+  </si>
+  <si>
+    <t>525 21st St</t>
+  </si>
+  <si>
     <t>https://www.va.gov/san-francisco-health-care/locations/twenty-first-street-va-clinic/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Dignity+Health+-+St.+Joseph%27s+Behavioral+Health+Center/data=!4m7!3m6!1s0x80900d6b65c420db:0xa3ba2da7a17fc268!8m2!3d37.9765743!4d-121.2910818!16s%2Fg%2F1tdxl368!19sChIJ2yDEZWsNkIARaMJ_oactuqM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Dignity Health - St. Joseph's Behavioral Health Center</t>
+  </si>
+  <si>
+    <t>2510 N California St</t>
+  </si>
+  <si>
     <t>https://www.dignityhealth.org/central-california/locations/stjosephsbehavioral</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Monterey+County+Behavioral+Health/data=!4m7!3m6!1s0x808df87b7d41b04f:0x7f2a7d5e0004c0ef!8m2!3d36.6556733!4d-121.637022!16s%2Fg%2F1tk1z88s!19sChIJT7BBfXv4jYAR78AEAF59Kn8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Monterey County Behavioral Health</t>
+  </si>
+  <si>
+    <t>Public health department</t>
+  </si>
+  <si>
+    <t>951 Blanco Cir # B</t>
+  </si>
+  <si>
     <t>http://www.mtyhd.org/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/San+Benito+County+Behavioral+Health/data=!4m7!3m6!1s0x8091f64cd0969dad:0xb1e8a174eb5cc76!8m2!3d36.8729811!4d-121.3980091!16s%2Fg%2F11c46lx0qf!19sChIJrZ2W0Ez2kYARdsy1TheKHgs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>San Benito County Behavioral Health</t>
+  </si>
+  <si>
+    <t>1131 Community Pkwy</t>
+  </si>
+  <si>
     <t>https://www.cosb.us/departments/behavioral-health</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Santa+Cruz+Behavioral+Health+Division/data=!4m7!3m6!1s0x808e404080a4e685:0xd8975005e88cf2e8!8m2!3d36.992828!4d-122.018133!16s%2Fg%2F1vm7bpm4!19sChIJheakgEBAjoAR6PKM6AVQl9g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Santa Cruz Behavioral Health Division</t>
+  </si>
+  <si>
+    <t>1400 Emeline Ave #1976</t>
+  </si>
+  <si>
     <t>http://www.santacruzhealth.org/HSAHome/HSADivisions/BehavioralHealth.aspx</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Behavioral+Healthcare+Partners/data=!4m7!3m6!1s0x80dc73e1dcb98bcd:0xacf1a316f14f5273!8m2!3d33.1847454!4d-117.2877758!16s%2Fg%2F11gzpqy3_!19sChIJzYu53OFz3IARc1JP8Raj8aw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Behavioral Healthcare Partners</t>
+  </si>
+  <si>
+    <t>Counselor</t>
+  </si>
+  <si>
+    <t>2095 W Vista Way</t>
+  </si>
+  <si>
     <t>http://vistatherapists.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Central+California+Alliance+for+Health/data=!4m7!3m6!1s0x808e40b4808e5165:0x381af436972546b9!8m2!3d37.050252!4d-122.010003!16s%2Fg%2F1tcwg69m!19sChIJZVGOgLRAjoARuUYllzb0Gjg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Central California Alliance for Health</t>
+  </si>
+  <si>
+    <t>1600 Green Hills Rd #101</t>
+  </si>
+  <si>
     <t>https://thealliance.health/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Behavioral+Health+Center/data=!4m7!3m6!1s0x809057a6cd57a857:0xa0e7e9405906b3a1!8m2!3d37.6879765!4d-120.976446!16s%2Fg%2F11ry6qcr69!19sChIJV6hXzaZXkIARobMGWUDp56A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Behavioral Health Center</t>
+  </si>
+  <si>
+    <t>Medical Center</t>
+  </si>
+  <si>
+    <t>3425 Coffee Rd Suite 2A</t>
+  </si>
+  <si>
     <t>https://www.sutterhealth.org/find-location/facility/behavioral-health-center-1043246992</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/California+Health+Care+Foundation/data=!4m7!3m6!1s0x808f80b47f8da505:0x92c6dd60b9b99a72!8m2!3d37.8037491!4d-122.2680054!16s%2Fg%2F1thw6zg1!19sChIJBaWNf7SAj4ARcpq5uWDdxpI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>California Health Care Foundation</t>
+  </si>
+  <si>
+    <t>1438 Webster St #400</t>
+  </si>
+  <si>
     <t>http://www.chcf.org/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Tuolumne+County+Behavioral+Health/data=!4m7!3m6!1s0x8090c5c7e164eb0f:0x18440c013d07fc8!8m2!3d37.9743128!4d-120.3778115!16s%2Fg%2F1vhkksty!19sChIJD-tk4cfFkIARyH_QE8BAhAE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Tuolumne County Behavioral Health</t>
+  </si>
+  <si>
+    <t>105 Hospital Rd</t>
+  </si>
+  <si>
     <t>https://www.tuolumnecounty.ca.gov/220/Behavioral-Health</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Family+Behavioral+Health/data=!4m7!3m6!1s0x809467d71d43d865:0x310323b79c4ed9da!8m2!3d36.8238894!4d-119.7563118!16s%2Fg%2F1th0ylr7!19sChIJZdhDHddnlIAR2tlOnLcjAzE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Family Behavioral Health</t>
+  </si>
+  <si>
+    <t>Psychotherapist</t>
+  </si>
+  <si>
+    <t>1704 E Bullard Ave</t>
+  </si>
+  <si>
     <t>http://www.counselingfresno.net/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Santa+Clara+Family+Health+Plan/data=!4m7!3m6!1s0x808e3505b0c9d231:0xe6934fce1a8888a8!8m2!3d37.235691!4d-121.7761764!16s%2Fg%2F1w6_p19r!19sChIJMdLJsAU1joARqIiIGs5Pk-Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Santa Clara Family Health Plan</t>
+  </si>
+  <si>
+    <t>6201 San Ignacio Ave</t>
+  </si>
+  <si>
     <t>https://www.scfhp.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/River+Vista+Behavioral+Health/data=!4m7!3m6!1s0x80940f622ce7a457:0xc3c67a1ad7d012!8m2!3d36.8832123!4d-119.8044605!16s%2Fg%2F11qgdj5l6c!19sChIJV6TnLGIPlIAREtDXGnrGwwA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>River Vista Behavioral Health</t>
+  </si>
+  <si>
+    <t>40886 Goodwin Way</t>
+  </si>
+  <si>
     <t>https://rivervistabh.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Kings+County+Behavioral+Health/data=!4m7!3m6!1s0x87b781ec0ab42ea5:0x7c3f91960421c005!8m2!3d36.3285181!4d-119.664647!16s%2Fg%2F11cmslq3gk!19sChIJpS60CuyBt4cRBcAhBJaRP3w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Kings County Behavioral Health</t>
+  </si>
+  <si>
+    <t>1222 W Lacey Blvd 2nd Floor</t>
+  </si>
+  <si>
     <t>http://www.kcbh.org/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/California+Health+Collaborative/data=!4m7!3m6!1s0x8091433f8f918e97:0xb1396659075ecf5f!8m2!3d37.3187533!4d-120.488301!16s%2Fg%2F11lgvwf5x6!19sChIJl46Rjz9DkYARX89eB1lmObE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>California Health Collaborative</t>
+  </si>
+  <si>
+    <t>1180 W Olive Ave Ste K</t>
+  </si>
+  <si>
     <t>http://www.kadiant.com/central-valley-services</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Central+Coast+Behavioral+Health/data=!4m7!3m6!1s0x8b27979a1fb64735:0x50cd9e43df9c5b42!8m2!3d36.8389902!4d-119.7797213!16s%2Fg%2F11vr4m4vc6!19sChIJNUe2H5qXJ4sRQluc30OezVA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Central Coast Behavioral Health</t>
+  </si>
+  <si>
+    <t>Psychiatrist</t>
+  </si>
+  <si>
+    <t>7067 N Mariposa St Ste 103</t>
+  </si>
+  <si>
     <t>https://www.mindvibe.com/location/california/fresno/?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=business_profile&amp;utm_content=fresno</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Santa+Clara+County+Behavioral+Health+Services/data=!4m7!3m6!1s0x808fcb33fcc7b31d:0x9111bb1203c91389!8m2!3d37.312217!4d-121.9311668!16s%2Fg%2F1tv24cyz!19sChIJHbPH_DPLj4ARiRPJAxK7EZE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Santa Clara County Behavioral Health Services</t>
+  </si>
+  <si>
+    <t>828 S Bascom Ave</t>
+  </si>
+  <si>
     <t>http://www.sccbhsd.org/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Adventist+Health+Behavioral+Health/data=!4m7!3m6!1s0x8090c5eba8fb21b1:0xfaee685a5145c983!8m2!3d37.9789917!4d-120.3911811!16s%2Fg%2F11vst8p1n1!19sChIJsSH7qOvFkIARg8lFUVpo7vo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Medical clinic</t>
+  </si>
+  <si>
+    <t>193 S Fairview Ln Ste K</t>
+  </si>
+  <si>
     <t>https://adventisthealth.org/locations/detail/primary-care-behavioral-health-adventist-health-sonora/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/SoCal+Empowered/data=!4m7!3m6!1s0x80dce92d085274dd:0x5bdd97463a79fd1d!8m2!3d33.6343062!4d-117.694228!16s%2Fg%2F11hz087hmb!19sChIJ3XRSCC3p3IARHf15OkaX3Vs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>SoCal Empowered</t>
+  </si>
+  <si>
+    <t>Â·</t>
+  </si>
+  <si>
     <t>https://socalempowered.com/?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=gbpsocal</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Sutter+Alta+Bates+Summit+Medical+Center:+Behavioral+Health+Center+of+Excellence/data=!4m7!3m6!1s0x80857e83109b6565:0xfba52f776bf588e!8m2!3d37.8641988!4d-122.2685144!16s%2Fg%2F11b7tr0y38!19sChIJZWWbEIN-hYARjli_dvdSug8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Sutter Alta Bates Summit Medical Center: Behavioral Health Center of Excellence</t>
+  </si>
+  <si>
+    <t>2001 Dwight Way Ste 4190</t>
+  </si>
+  <si>
     <t>http://www.altabatessummit.org/behavhealth/?utm_medium=local&amp;utm_source=google_plus-local&amp;utm_campaign=local-Berkeley-SAB-8</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Adventist+Health+Primary+Care/data=!4m7!3m6!1s0x8090c539ccd66ae3:0xa76ad702875b4864!8m2!3d37.9788015!4d-120.3907926!16s%2Fg%2F11r3dthy4q!19sChIJ42rWzDnFkIARZEhbhwLXaqc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Adventist Health Primary Care</t>
+  </si>
+  <si>
+    <t>193 S Fairview Ln B</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Community+Behavioral+Health+Services/data=!4m7!3m6!1s0x808f7dcdb150f365:0x524b8c0971c4560d!8m2!3d37.7711627!4d-122.4193292!16s%2Fg%2F1tcxj_9n!19sChIJZfNQsc19j4ARDVbEcQmMS1I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Community Behavioral Health Services</t>
+  </si>
+  <si>
+    <t>1663 Mission St #460</t>
+  </si>
+  <si>
     <t>https://www.cbh.us/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Peninsula+Behavioral+Health/data=!4m7!3m6!1s0x808fbb3ed2f22043:0x154e5a613e011577!8m2!3d37.4219843!4d-122.1362792!16s%2Fg%2F11c609n3wj!19sChIJQyDy0j67j4ARdxUBPmFaThU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Peninsula Behavioral Health</t>
+  </si>
+  <si>
+    <t>3260 Ash St</t>
+  </si>
+  <si>
     <t>https://www.penbh.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Madera+County+Behavioral+Health/data=!4m7!3m6!1s0x80940cf3df7de049:0xcffed2536f5dbd8e!8m2!3d36.9609071!4d-120.0562264!16s%2Fg%2F1v44f69k!19sChIJSeB93_MMlIARjr1db1PS_s8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Madera County Behavioral Health</t>
+  </si>
+  <si>
+    <t>209 E 7th St</t>
+  </si>
+  <si>
     <t>http://www.madera-county.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/California+Health+%26+Wellness/data=!4m7!3m6!1s0x809ad0d7c918ea35:0x4e05d0daa4c9f8fc!8m2!3d38.6091194!4d-121.4988683!16s%2Fg%2F11c0r0vh9g!19sChIJNeoYydfQmoAR_PjJpNrQBU4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>California Health &amp; Wellness</t>
+  </si>
+  <si>
+    <t>1740 Creekside Oaks Dr #200</t>
+  </si>
+  <si>
     <t>https://www.cahealthwellness.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Stanislaus+County+Behavioral+Health+Wellness+Recovery+Center/data=!4m7!3m6!1s0x809053dec75ecc83:0xa83bb1064ddd4dee!8m2!3d37.6510282!4d-121.0149402!16s%2Fg%2F11bt_jwg5l!19sChIJg8xex95TkIAR7k3dTQaxO6g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Stanislaus County Behavioral Health Wellness Recovery Center</t>
+  </si>
+  <si>
+    <t>500 N 9th St A</t>
+  </si>
+  <si>
     <t>http://www.stancounty.com/bhrs/services-adult.shtm</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Blue+Shield+Promise+Health+Plan+-+Informational+Resource+Center/data=!4m7!3m6!1s0x80c2c9212f73115d:0xf2cfa7d2be754520!8m2!3d33.9882328!4d-118.2248741!16s%2Fg%2F1tjhxy8w!19sChIJXRFzLyHJwoARIEV1vtKnz_I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Blue Shield Promise Health Plan - Informational Resource Center</t>
+  </si>
+  <si>
+    <t>5926 Pacific Blvd</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/CalOptima+Health/data=!4m7!3m6!1s0x80dcd9c54393c3c3:0x10152464776609c9!8m2!3d33.7833541!4d-117.8957931!16s%2Fg%2F1tf07zcp!19sChIJw8OTQ8XZ3IARyQlmd2QkFRA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>CalOptima Health</t>
+  </si>
+  <si>
     <t>https://www.caloptima.org/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Beyond+Behavior+California/data=!4m7!3m6!1s0x809041fd9a9861a3:0x68aa6d9b8b201f81!8m2!3d37.8003369!4d-121.2304152!16s%2Fg%2F11pclg0qvx!19sChIJo2GYmv1BkIARgR8gi5ttqmg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Beyond Behavior California</t>
+  </si>
+  <si>
+    <t>Home health care service</t>
+  </si>
+  <si>
+    <t>250 Cherry Ln Ste 109</t>
+  </si>
+  <si>
     <t>http://beyondbehaviorcalifornia.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Merced+Behavioral+Health+Center/data=!4m7!3m6!1s0x809143184fe12589:0x4fa83a0e1057d44a!8m2!3d37.2905644!4d-120.4722606!16s%2Fg%2F1v9lc05q!19sChIJiSXhTxhDkYARStRXEA46qE8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Merced Behavioral Health Center</t>
+  </si>
+  <si>
+    <t>1255 B St</t>
+  </si>
+  <si>
     <t>https://mercedbehavioral.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Bio-Behavioral+Medical+Clinics,+Inc./data=!4m7!3m6!1s0x8094680aee230a99:0x1ab69ded23806666!8m2!3d36.8304182!4d-119.8099542!16s%2Fg%2F1tj1mr_b!19sChIJmQoj7gpolIARZmaAI-2dtho?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Bio-Behavioral Medical Clinics, Inc.</t>
+  </si>
+  <si>
+    <t>1060 W Sierra Ave #104</t>
+  </si>
+  <si>
     <t>http://www.bbmc-inc.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Bay+Area+Mental+Health/data=!4m7!3m6!1s0x808e35e7b04462b7:0xc6c7fa23d344399c!8m2!3d37.2890399!4d-121.9502634!16s%2Fg%2F11b746rcnh!19sChIJt2JEsOc1joARnDlE0yP6x8Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Bay Area Mental Health</t>
+  </si>
+  <si>
+    <t>1925 Winchester Blvd #204</t>
+  </si>
+  <si>
     <t>https://www.bayareamh.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Contra+Costa+Behavioral+Health+Services/data=!4m7!3m6!1s0x808565cf0ed8dafb:0x4b1eda4d93379a88!8m2!3d37.9926237!4d-122.09878!16s%2Fg%2F1tg7s7cx!19sChIJ-9rYDs9lhYARiJo3k03aHks?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Contra Costa Behavioral Health Services</t>
+  </si>
+  <si>
+    <t>1340 Arnold Dr #200</t>
+  </si>
+  <si>
     <t>https://www.cchealth.org/services-and-programs/behavioral-health</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Ascend+Behavioral+Health/data=!4m7!3m6!1s0x80945d5d6243d62f:0x5c687426f3dd96ee!8m2!3d36.8388329!4d-119.7504579!16s%2Fg%2F11h5wl75sf!19sChIJL9ZDYl1dlIAR7pbd8yZ0aFw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Ascend Behavioral Health</t>
+  </si>
+  <si>
+    <t>1781 E Fir Ave Ste 101</t>
+  </si>
+  <si>
     <t>https://ascendbh.com/?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=gbp&amp;utm_content=fresno</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Valle+De+Salinas+Behavioral+Health/data=!4m7!3m6!1s0x808df9f6a7da840b:0xa4c09fdd1ac1a2f7!8m2!3d36.6582827!4d-121.6474051!16s%2Fg%2F11ld350tgg!19sChIJC4Tap_b5jYAR96LBGt2fwKQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Valle De Salinas Behavioral Health</t>
+  </si>
+  <si>
+    <t>220 San Jose St</t>
+  </si>
+  <si>
     <t>https://vdsbehavioralhealth.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Calaveras+County+Behavioral+Health/data=!4m7!3m6!1s0x80909b09a151a65f:0x9fc2f7ee71d981ae!8m2!3d38.190258!4d-120.6652735!16s%2Fg%2F1tykvmgs!19sChIJX6ZRoQmbkIARroHZce73wp8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Calaveras County Behavioral Health</t>
+  </si>
+  <si>
+    <t>891 Mountain Ranch Rd Building M</t>
+  </si>
+  <si>
     <t>http://mentalhealth.calaverasgov.us/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Kaiser+Permanente+Behavioral+Health+Center/data=!4m7!3m6!1s0x808fb58eff761f03:0xcb6a3171daeff6fa!8m2!3d37.3362819!4d-122.0018783!16s%2Fg%2F11btxhd376!19sChIJAx92_461j4AR-vbv2nExass?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Kaiser Permanente Behavioral Health Center</t>
+  </si>
+  <si>
+    <t>3840 Homestead Rd</t>
+  </si>
+  <si>
     <t>https://healthy.kaiserpermanente.org/southern-california/front-door</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Ohana+Center+for+Child+and+Adolescent+Behavioral+Health/data=!4m7!3m6!1s0x808de52a8b8d6ea7:0x5a46976d44f6eb7!8m2!3d36.5752499!4d-121.820136!16s%2Fg%2F11rg79p0dw!19sChIJp26NiyrljYARt25P1HZppAU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Ohana Center for Child and Adolescent Behavioral Health</t>
+  </si>
+  <si>
+    <t>6 Lower Ragsdale Dr</t>
+  </si>
+  <si>
     <t>https://www.montagehealth.org/locations/profile/ohana</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Valley+Health+Plan/data=!4m7!3m6!1s0x808fcbde01e1b301:0x33e2b97c2fab6d66!8m2!3d37.2612279!4d-121.7864181!16s%2Fg%2F125_swtn0!19sChIJAbPhAd7Lj4ARZm2rL3y54jM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Valley Health Plan</t>
+  </si>
+  <si>
+    <t>5845 Hellyer Ave</t>
+  </si>
+  <si>
     <t>http://www.valleyhealthplan.org/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Nucleus+Behavioral+Health/data=!4m7!3m6!1s0x809467f3bf5cf8c3:0x87e3815caeeb6192!8m2!3d36.8097496!4d-119.8163302!16s%2Fg%2F11pf7czm3t!19sChIJw_hcv_NnlIARkmHrrlyB44c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Nucleus Behavioral Health</t>
+  </si>
+  <si>
+    <t>Psychologist</t>
+  </si>
+  <si>
+    <t>5080 N Fruit Ave #102</t>
+  </si>
+  <si>
     <t>http://www.nucleusbehavioralhealth.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Kaiser+Permanente+Behavioral+Health+Clinic/data=!4m7!3m6!1s0x809015b9d86e7511:0x979513edf44a349e!8m2!3d37.8078039!4d-121.2954136!16s%2Fg%2F11rvd71dhp!19sChIJEXVu2LkVkIARnjRK9O0TlZc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Kaiser Permanente Behavioral Health Clinic</t>
+  </si>
+  <si>
+    <t>17000 S Harlan Rd</t>
+  </si>
+  <si>
     <t>https://healthy.kaiserpermanente.org/northern-california/facilities/lathrop-mental-health-and-wellness-center-425177</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Merced+County+Behavioral+Health+and+Recovery+Services/data=!4m7!3m6!1s0x80914319cde3ff6f:0x61d64eca4dd2e6f2!8m2!3d37.2934329!4d-120.4738128!16s%2Fg%2F1tm1qq9r!19sChIJb__jzRlDkYAR8ubSTcpO1mE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Merced County Behavioral Health and Recovery Services</t>
+  </si>
+  <si>
+    <t>301 E 13th St</t>
+  </si>
+  <si>
     <t>https://www.co.merced.ca.us/78/Behavioral-Health-and-Recovery-Services</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Trumpet+Behavioral+Health,+a+division+of+BlueSprig/data=!4m7!3m6!1s0x808f8774c66f55c3:0xe24d50027639299c!8m2!3d37.7822385!4d-122.2425006!16s%2Fg%2F11rcsbwzzl!19sChIJw1VvxnSHj4ARnCk5dgJQTeI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Trumpet Behavioral Health, a division of BlueSprig</t>
+  </si>
+  <si>
+    <t>Child health care center</t>
+  </si>
+  <si>
+    <t>1944 Embarcadero</t>
+  </si>
+  <si>
     <t>https://www.bluesprigautism.com/centers/california/oakland/?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=gbp</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Avante+Behavioral+Health/data=!4m7!3m6!1s0x80945d4bba9b3503:0x35fc30d8d4ad82ca!8m2!3d36.8116226!4d-119.7629161!16s%2Fg%2F1tfd2n5h!19sChIJAzWbuktdlIARyoKt1Ngw_DU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Avante Behavioral Health</t>
+  </si>
+  <si>
+    <t>5150 N 6th St #156</t>
+  </si>
+  <si>
     <t>http://www.avantehealth.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Redwood+Behavioral+Health/data=!4m7!3m6!1s0x8085bd1d60c742ff:0xe714081b68e701b2!8m2!3d38.1044154!4d-122.5700325!16s%2Fg%2F11y39kw0f9!19sChIJ_0LHYB29hYARsgHnaBsIFOc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Redwood Behavioral Health</t>
+  </si>
+  <si>
+    <t>7250 Redwood Blvd Suite 300</t>
+  </si>
+  <si>
     <t>https://www.redwoodbehavioralhealth.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Livewell+Behavioral+Health+Counseling+Center/data=!4m7!3m6!1s0x80945d72d45f9cf9:0x81c0211e54bcc0c0!8m2!3d36.8092445!4d-119.7659935!16s%2Fg%2F11d_793f3r!19sChIJ-Zxf1HJdlIARwMC8VB4hwIE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Livewell Behavioral Health Counseling Center</t>
+  </si>
+  <si>
+    <t>1300 E Shaw Ave #149</t>
+  </si>
+  <si>
     <t>http://www.livewellbhc.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Monterey+County+Behavioral+Health/data=!4m7!3m6!1s0x808dfde1bcdbbd65:0xcbda372427102f3f!8m2!3d36.6683762!4d-121.8009787!16s%2Fg%2F11rd01zz4v!19sChIJZb3bvOH9jYARPy8QJyQ32ss?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>299 Twelfth St</t>
+  </si>
+  <si>
     <t>https://www.countyofmonterey.gov/government/departments-a-h/health/behavioral-health</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Behavioral+Health+Quest/data=!4m7!3m6!1s0x808fe913ad39bc5d:0x1ea4f1791dc2d3ed!8m2!3d37.6823181!4d-121.8749736!16s%2Fg%2F1tk1z8n0!19sChIJXbw5rRPpj4AR7dPCHXnxpB4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Behavioral Health Quest</t>
+  </si>
+  <si>
+    <t>2324 Santa Rita Rd #10</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+Behavioral+Health/data=!4m7!3m6!1s0x809143a7ad598d67:0x82fa715c8126861e!8m2!3d37.3115926!4d-120.4688419!16s%2Fg%2F1tcw3w49!19sChIJZ41ZradDkYARHoYmgVxx-oI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>50 Alpine Dr</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/San+Joaquin+County+Behavioral+Health+Services/data=!4m7!3m6!1s0x80900d646847901f:0xdaddfee1e8878541!8m2!3d37.9642945!4d-121.2932301!16s%2Fg%2F11bychxsnq!19sChIJH5BHaGQNkIARQYWH6OH-3do?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>1149 N El Dorado St</t>
+  </si>
+  <si>
     <t>http://www.sjgov.org/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Vitalize+Behavioral+Health/data=!4m7!3m6!1s0x8094437796f1f8dd:0x4a24aaac81960326!8m2!3d36.8423491!4d-119.7767057!16s%2Fg%2F11shs7c0wt!19sChIJ3fjxlndDlIARJgOWgayqJEo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Vitalize Behavioral Health</t>
+  </si>
+  <si>
+    <t>7265 N First St Ste 103</t>
+  </si>
+  <si>
     <t>http://www.vitalizepsych.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Community+Behavioral+Health/data=!4m7!3m6!1s0x8085135530556bd3:0x184afb7d80888351!8m2!3d38.2213242!4d-122.1392104!16s%2Fg%2F11vs_86y17!19sChIJ02tVMFUThYARUYOIgH37Shg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Community Behavioral Health</t>
+  </si>
+  <si>
+    <t>4820 Business Center Dr Suite 110</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Behavioral+Health/data=!4m7!3m6!1s0x808df8abf48402f9:0x5a5c92b8cc3583c4!8m2!3d36.6960956!4d-121.6336821!16s%2Fg%2F11clzgh91n!19sChIJ-QKE9Kv4jYARxIM1zLiSXFo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Behavioral Health</t>
+  </si>
+  <si>
+    <t>1270 Medical Center Dr</t>
+  </si>
+  <si>
     <t>https://www.countyofmonterey.gov/government/departments-a-h/health/behavioral-health/bh-home</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Central+Star+Behavioral+Health,+Inc./data=!4m7!3m6!1s0x80945e5a6c584c05:0x818fd18ff15c3508!8m2!3d36.7384438!4d-119.7503342!16s%2Fg%2F11hy9nnkh2!19sChIJBUxYbFpelIARCDVc8Y_Rj4E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Central Star Behavioral Health, Inc.</t>
+  </si>
+  <si>
+    <t>496 S Barton Ave</t>
+  </si>
+  <si>
     <t>https://www.starsinc.com/fresno-county/the-fresno-crt/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Mental+Health+Insurance+Billing+Inc/data=!4m7!3m6!1s0x808e3ff9addeaaab:0x783c32b14bc3d76f!8m2!3d36.9859291!4d-122.008491!16s%2Fg%2F11h1lvh40z!19sChIJq6rerfk_joARb9fDS7EyPHg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Mental Health Insurance Billing Inc</t>
+  </si>
+  <si>
+    <t>Medical billing service</t>
+  </si>
+  <si>
+    <t>103 Parnell St</t>
+  </si>
+  <si>
     <t>http://mentalhealthbill.net/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Adventist+Health+Behavioral+Health/data=!4m7!3m6!1s0x8094f17a566e7ab9:0xa569be7cf2756168!8m2!3d36.5703675!4d-119.614121!16s%2Fg%2F11zy3f4x2y!19sChIJuXpuVnrxlIARaGF18ny-aaU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
     <t>https://www.adventisthealth.org/central-california/locations/adventist-health-behavioral-health-2141-high-street-suite-b/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Madera+County+Behavioral/data=!4m7!3m6!1s0x80940b823fd3f19b:0x52871e3c2ca5b5f2!8m2!3d36.9537455!4d-120.0736312!16s%2Fg%2F1vp740bx!19sChIJm_HTP4ILlIAR8rWlLDweh1I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Madera County Behavioral</t>
+  </si>
+  <si>
+    <t>117 N R St #101</t>
+  </si>
+  <si>
     <t>https://www.maderacounty.com/government/behavioral-health-services</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Outpatient+Behavioral+Health+Services/data=!4m7!3m6!1s0x808de687e280bfed:0x4b6583693c6bc039!8m2!3d36.5952364!4d-121.8959268!16s%2Fg%2F1tj96nc4!19sChIJ7b-A4ofmjYAROcBrPGmDZUs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Outpatient Behavioral Health Services</t>
+  </si>
+  <si>
+    <t>576 Hartnell St</t>
+  </si>
+  <si>
     <t>https://www.montagehealth.org/locations/profile/behavioral-services</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/California+School-Based+Health+Alliance/data=!4m7!3m6!1s0x808f80baa4daecb7:0x4a28f52f918bbaef!8m2!3d37.805369!4d-122.277602!16s%2Fg%2F1tdm_r56!19sChIJt-zapLqAj4AR77qLkS_1KEo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>California School-Based Health Alliance</t>
+  </si>
+  <si>
+    <t>1203 Preservation Park Way #302</t>
+  </si>
+  <si>
     <t>http://www.schoolhealthcenters.org/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Building+Connections+Behavioral+Health,+INC/data=!4m7!3m6!1s0x808f8cb4db69b9c9:0xc1670752bbb4628f!8m2!3d37.8972086!4d-122.0564892!16s%2Fg%2F11clwhhygw!19sChIJyblp27SMj4ARj2K0u1IHZ8E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Building Connections Behavioral Health, INC</t>
+  </si>
+  <si>
+    <t>710 S Broadway Ste 250</t>
+  </si>
+  <si>
     <t>http://www.bcbhinc.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Central+Star+Behavioral/data=!4m7!3m6!1s0x80945d581f8661f9:0xb88f989fc0ac8321!8m2!3d36.777731!4d-119.7807733!16s%2Fg%2F11gwfzsp0j!19sChIJ-WGGH1hdlIARIYOswJ-Yj7g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Central Star Behavioral</t>
+  </si>
+  <si>
     <t>https://www.starsinc.com/fresno-county/central-star-behavioral-health/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Vitalize+Behavioral+Health/data=!4m7!3m6!1s0x80945bf339a3e003:0xcbdcda62f338fb28!8m2!3d36.8087036!4d-119.8112855!16s%2Fg%2F11lkysctkv!19sChIJA-CjOfNblIARKPs482La3Ms?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>1100 W Shaw Ave #112</t>
+  </si>
+  <si>
     <t>http://vitalizepsych.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/John+Muir+Health+Psychiatric+Hospital/data=!4m7!3m6!1s0x8085671feb1dcce7:0x1d0a484d58d1dac0!8m2!3d37.9859062!4d-122.036857!16s%2Fg%2F1tfl9wsk!19sChIJ58wd6x9nhYARwNrRWE1ICh0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>John Muir Health Psychiatric Hospital</t>
+  </si>
+  <si>
+    <t>Psychiatric hospital</t>
+  </si>
+  <si>
+    <t>2740 Grant St</t>
+  </si>
+  <si>
     <t>https://www.johnmuirhealth.com/services/behavioral-health-services/psychiatric-hospital.html</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/South+Bay+Behavioral+Health/data=!4m7!3m6!1s0x808e358700cecb71:0x9ca176c596119569!8m2!3d37.224458!4d-121.9837233!16s%2Fg%2F11t_tj6xhj!19sChIJccvOAIc1joARaZURlsV2oZw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>South Bay Behavioral Health</t>
+  </si>
+  <si>
+    <t>213 Bean Ave</t>
+  </si>
+  <si>
     <t>https://southbaybh.net/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Crestwood+Behavioral+Health/data=!4m7!3m6!1s0x808fb69eabc00001:0xa52225f880f7afda!8m2!3d37.3516513!4d-122.0556013!16s%2Fg%2F11y2r5_dkm!19sChIJAQDAq562j4AR2q_3gPglIqU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Crestwood Behavioral Health</t>
+  </si>
+  <si>
+    <t>1002 W Fremont Ave</t>
+  </si>
+  <si>
     <t>https://crestwoodbehavioralhealth.com/location/sunnyvale/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/NAMI+California/data=!4m7!3m6!1s0x809ada4081822e5b:0x71f752a2fb8ff272!8m2!3d38.5700519!4d-121.4178716!16s%2Fg%2F11b6vdvsjz!19sChIJWy6CgUDamoARcvKP-6JS93E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>NAMI California</t>
+  </si>
+  <si>
+    <t>425 University Ave</t>
+  </si>
+  <si>
     <t>https://www.namica.org/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Synergy+Behavioral+Mental+Health+and+Wellness+Care/data=!4m7!3m6!1s0x6cc397eafc8151e9:0xcfed9facc4fed36c!8m2!3d37.2695056!4d-119.306607!16s%2Fg%2F11zbjv24p3!19sChIJ6VGB_OqXw2wRbNP-xKyf7c8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Synergy Behavioral Mental Health and Wellness Care</t>
+  </si>
+  <si>
     <t>http://www.synergybehavioral.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Crestwood+Behavioral+Health/data=!4m7!3m6!1s0x8094e42effd448bd:0x6c030b58157b5bab!8m2!3d36.5134058!4d-119.5484834!16s%2Fg%2F11b7fch__y!19sChIJvUjU_y7klIARq1t7FVgLA2w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>1200 Smith St</t>
+  </si>
+  <si>
     <t>https://crestwoodbehavioralhealth.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/San+Luis+Obispo+County:+Behavioral+Health+North+County:+Youth+%26+Adults/data=!4m7!3m6!1s0x80ecc27da9ef3463:0x775ce20c39f79295!8m2!3d35.492616!4d-120.6628697!16s%2Fg%2F1tgwskz_!19sChIJYzTvqX3C7IARlZL3OQziXHc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>San Luis Obispo County: Behavioral Health North County: Youth &amp; Adults</t>
+  </si>
+  <si>
+    <t>5575 Hospital Dr</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clear+Behavioral+Health+-+Virtual+Mental+Health+Treatment+for+Teens+%26+Adults/data=!4m7!3m6!1s0x809051eebdb4f499:0x580f13792a7889f3!8m2!3d37.6591791!4d-121.0291911!16s%2Fg%2F11n0b0vwvk!19sChIJmfS0ve5RkIAR84l4KnkTD1g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Clear Behavioral Health - Virtual Mental Health Treatment for Teens &amp; Adults</t>
+  </si>
+  <si>
+    <t>1600 N Carpenter Rd e1</t>
+  </si>
+  <si>
     <t>https://clearbehavioralhealth.com/locations/virtual-mental-health-services-california/?utm_source=GBP&amp;utm_medium=Listing&amp;utm_campaign=Modesto</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Portia+Bell+Hume+Behavioral+Health+and+Training+Center:+CC+Central/data=!4m7!3m6!1s0x808566cf766a1a6f:0xeb93049f3b49fa9!8m2!3d37.9699037!4d-122.052195!16s%2Fg%2F1tj52txt!19sChIJbxpqds9mhYARqZ-080kwuQ4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Portia Bell Hume Behavioral Health and Training Center: CC Central</t>
+  </si>
+  <si>
+    <t>1333 Willow Pass Rd #102</t>
+  </si>
+  <si>
     <t>http://www.humecenter.org/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Blue+Wave+Behavioral+Health/data=!4m7!3m6!1s0x808e352a1c73884f:0xad058ada40a16d32!8m2!3d37.2877354!4d-121.9486887!16s%2Fg%2F11x0zy1ynn!19sChIJT4hzHCo1joARMm2hQNqKBa0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Blue Wave Behavioral Health</t>
+  </si>
+  <si>
+    <t>51 E Campbell Ave Ste 101-A</t>
+  </si>
+  <si>
     <t>https://onewaveatatime.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Central+Star+Behavioral+Health/data=!4m7!3m6!1s0x809051420a4864cd:0xa2ac6dca5e7e6b6c!8m2!3d37.666831!4d-120.9947569!16s%2Fg%2F11f5v0pknf!19sChIJzWRICkJRkIARbGt-XsptrKI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Central Star Behavioral Health</t>
+  </si>
+  <si>
+    <t>1539 McHenry Ave</t>
+  </si>
+  <si>
     <t>http://www.starsinc.com/stanislaus-county/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Concordis+Behavioral+Health+-+Walnut+Creek/data=!4m7!3m6!1s0x8085616ce0a0c06f:0x41175fddc3cc1ec9!8m2!3d37.8918611!4d-122.0568!16s%2Fg%2F11w92805br!19sChIJb8Cg4GxhhYARyR7Mw91fF0E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Concordis Behavioral Health - Walnut Creek</t>
+  </si>
+  <si>
+    <t>1460 Maria Ln #300</t>
+  </si>
+  <si>
     <t>https://www.concordisbh.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Central+Valley+Indian+Health+-+BHS/data=!4m7!3m6!1s0x80945be0fc8af261:0x6660a2bf17583c98!8m2!3d36.8232534!4d-119.7145305!16s%2Fg%2F11fktrg4qf!19sChIJYfKK_OBblIARmDxYF7-iYGY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Central Valley Indian Health - BHS</t>
+  </si>
+  <si>
+    <t>255 W Bullard Ave STE 101</t>
+  </si>
+  <si>
     <t>http://cvih.org/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/East+County+Childrens+Behavioral+Health/data=!4m7!3m6!1s0x808557c333e35173:0x5943c0f27ae91452!8m2!3d37.9709315!4d-121.784275!16s%2Fg%2F11h2l_ms26!19sChIJc1HjM8NXhYARUhTpevLAQ1k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>East County Childrens Behavioral Health</t>
+  </si>
+  <si>
+    <t>2335 Country Hls Dr</t>
+  </si>
+  <si>
     <t>https://www.cchealth.org/get-care/healthcare-locations/mental-health-clinics/east-county-children-s-behavioral-health</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Embark+Behavioral+Health/data=!4m7!3m6!1s0x8091df3d83e5df5d:0x877a72f2a085a7a5!8m2!3d37.1077525!4d-121.5987805!16s%2Fg%2F11pybbt7vy!19sChIJXd_lgz3fkYARpaeFoPJyeoc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Embark Behavioral Health</t>
+  </si>
+  <si>
+    <t>1470 E Middle Ave</t>
+  </si>
+  <si>
     <t>https://www.embarkbh.com/locations/california/san-martin/?utm_source=gmb&amp;utm_medium=organic</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Mariposa+County+Behavioral+Health+and+Recovery+Services/data=!4m7!3m6!1s0x8096ba04777471d9:0xb4e4d1e2d5287267!8m2!3d37.4994306!4d-119.9841874!16s%2Fg%2F126413w62!19sChIJ2XF0dwS6loARZ3Io1eLR5LQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Mariposa County Behavioral Health and Recovery Services</t>
+  </si>
+  <si>
+    <t>5362 Lemee Lane</t>
+  </si>
+  <si>
     <t>http://www.mariposacounty.org/Directory.aspx?did=6</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/South+Bay+Behavioral+Health/data=!4m7!3m6!1s0x808fcd04a69cedf3:0x14881ebb05752aed!8m2!3d37.3615717!4d-121.8502277!16s%2Fg%2F11gfd324_5!19sChIJ8-2cpgTNj4AR7Sp1BbseiBQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>200 Jose Figueres Ave Ste 265</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/California+Coastal+Mental+Health/data=!4m7!3m6!1s0x80ecf1876d32678f:0x372a3f3835e184b8!8m2!3d35.2773648!4d-120.6493474!16s%2Fg%2F11sstxf71c!19sChIJj2cybYfx7IARuIThNTg_Kjc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>California Coastal Mental Health</t>
+  </si>
+  <si>
+    <t>1985 Johnson Ave</t>
+  </si>
+  <si>
     <t>http://www.ccmentalhealth.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Crestwood+Behavioral+Health/data=!4m7!3m6!1s0x808561680f4a9111:0xa5c8e08f06f1df22!8m2!3d37.9347858!4d-122.0724898!16s%2Fg%2F1tfwdqmb!19sChIJEZFKD2hhhYARIt_xBo_gyKU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>550 Patterson Blvd</t>
+  </si>
+  <si>
     <t>https://www.crestwoodbehavioralhealth.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Behavioral+Health+Services/data=!4m7!3m6!1s0x809012b976c50715:0xf035d216aa2e168b!8m2!3d37.9479148!4d-121.2772571!16s%2Fg%2F11ghr0j4pt!19sChIJFQfFdrkSkIARixYuqhbSNfA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Behavioral Health Services</t>
+  </si>
+  <si>
+    <t>620 Aurora St S</t>
+  </si>
+  <si>
     <t>http://www.sjcbhs.org/ContactUs.aspx</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Mental+Health+Billing+Services/data=!4m7!3m6!1s0x80c284be7f914413:0x6c22b177555ef5a!8m2!3d34.2921336!4d-118.5622362!16s%2Fg%2F1tvm30f7!19sChIJE0SRf76EwoARWu9VdRcrwgY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Mental Health Billing Services</t>
+  </si>
+  <si>
+    <t>12052 Turtle Springs Ln</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Go+behavioral+LLC+%7C+aba+therapy+fresno+%7C+Best+ABA+therapy+in+California+%28ages+1-18%29/data=!4m7!3m6!1s0x80946153e93ee54f:0x3ae676ca8a52a758!8m2!3d36.7388809!4d-119.7952161!16s%2Fg%2F11sz4bccbz!19sChIJT-U-6VNhlIARWKdSisp25jo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Go behavioral LLC | aba therapy fresno | Best ABA therapy in California (ages 1-18)</t>
+  </si>
+  <si>
+    <t>1444 Fulton St</t>
+  </si>
+  <si>
     <t>http://www.gobehavioral.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Contact+Crestwood+Behavioral+Health/data=!4m7!3m6!1s0x80945e1bc91aaaab:0x64e20130984807d2!8m2!3d36.7444667!4d-119.7807513!16s%2Fg%2F11twq35_jk!19sChIJq6oayRtelIAR0gdImDAB4mQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Contact Crestwood Behavioral Health</t>
+  </si>
+  <si>
+    <t>153 N U St</t>
+  </si>
+  <si>
     <t>https://crestwoodbehavioralhealth.com/location/fresno/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Portia+Bell+Hume+Behavioral+Health+and+Training+Center:+CC+West/data=!4m7!3m6!1s0x8085764b479bcd87:0x755797327a50cfe0!8m2!3d37.9909292!4d-122.329128!16s%2Fg%2F11fyzbxkdj!19sChIJh82bR0t2hYAR4M9QejKXV3U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Portia Bell Hume Behavioral Health and Training Center: CC West</t>
+  </si>
+  <si>
+    <t>3095 Richmond Pkwy Spc 201</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stanislaus+County+Behavioral+Health+and+Recovery+Services/data=!4m7!3m6!1s0x8090540b1191fc89:0x3144b656b8bbe63e!8m2!3d37.6470072!4d-120.9837347!16s%2Fg%2F11clzrhmvh!19sChIJifyREQtUkIARPua7uFa2RDE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Stanislaus County Behavioral Health and Recovery Services</t>
+  </si>
+  <si>
+    <t>800 Scenic Dr</t>
+  </si>
+  <si>
     <t>http://crowdproject.org/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Destiny+Behavioral+Health/data=!4m7!3m6!1s0x808ff39cc5f1c729:0xa7aa56b32ff7c9fa!8m2!3d37.7762232!4d-121.9699716!16s%2Fg%2F11xd2g8c94!19sChIJKcfxxZzzj4AR-sn3L7NWqqc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Destiny Behavioral Health</t>
+  </si>
+  <si>
+    <t>2250 Camino Ramon</t>
+  </si>
+  <si>
     <t>https://www.dbh.care/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Rogers+Behavioral+Health/data=!4m7!3m6!1s0x808560f88cafffff:0x1a09f0eead5ad3b4!8m2!3d37.9302894!4d-122.0302358!16s%2Fg%2F11hd6ny0xf!19sChIJ__-vjPhghYARtNNare7wCRo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Rogers Behavioral Health</t>
+  </si>
+  <si>
+    <t>420 N Wiget Ln Bldg 2</t>
+  </si>
+  <si>
     <t>https://rogersbh.org/locations/san-francisco-east-bay-ca</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/John+Muir+Health+Behavioral+Health+Center/data=!4m7!3m6!1s0x80856774c58cccad:0xf6f7a363eb7c27a4!8m2!3d38.0143027!4d-122.0242632!16s%2Fg%2F11j2fqd5zz!19sChIJrcyMxXRnhYARpCd862Oj9_Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>John Muir Health Behavioral Health Center</t>
+  </si>
+  <si>
+    <t>4080 Port Chicago Hwy</t>
+  </si>
+  <si>
     <t>https://www.johnmuirhealth.com/services/behavioral-health-services.html?cid=orgloc%3AwebsiteURL%3Ayext&amp;y_source=1_MTUzNzQyNDQtNzE1LWxvY2F0aW9uLndlYnNpdGU%3D</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/California+Behavior+Solutions+Inc/data=!4m7!3m6!1s0x808561487500a50d:0x7ff3be2fe164521f!8m2!3d37.9484411!4d-122.0616168!16s%2Fg%2F1tdcm5ll!19sChIJDaUAdUhhhYARH1Jk4S--838?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>California Behavior Solutions Inc</t>
+  </si>
+  <si>
+    <t>91 Gregory Ln</t>
+  </si>
+  <si>
     <t>http://www.eastbaytms.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/Traditions+Behavioral+Health/data=!4m7!3m6!1s0x8085065ce017a6a1:0xe9a2f47b33f2ab25!8m2!3d37.9486781!4d-122.5100742!16s%2Fg%2F1tj3l95_!19sChIJoaYX4FwGhYARJavyM3v0ouk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Traditions Behavioral Health</t>
+  </si>
+  <si>
+    <t>900 Larkspur Landing Cir</t>
+  </si>
+  <si>
     <t>https://tbhcare.com/</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/place/INS+Specialists+%26+Behavioral+Treatment/data=!4m7!3m6!1s0x808581309d7dc141:0x6e3b8d7712fb04cc!8m2!3d37.7887271!4d-122.4341478!16s%2Fg%2F11yzpb90wt!19sChIJQcF9nTCBhYARzAT7EneNO24?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>INS Specialists &amp; Behavioral Treatment</t>
+  </si>
+  <si>
+    <t>2417 California St</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Behavioral+Health+And+Recovery/data=!4m7!3m6!1s0x808f9e454cf16373:0x9d9523b89dffccb2!8m2!3d37.5449282!4d-122.3222348!16s%2Fg%2F113f9by83!19sChIJc2PxTEWej4ARssz_nbgjlZ0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Behavioral Health And Recovery</t>
+  </si>
+  <si>
+    <t>1950 Alameda de las Pulgas</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Behavioral+Health+Concepts,+Inc./data=!4m7!3m6!1s0x80857e5b4b645e7d:0x83a9b01a1dcbbf04!8m2!3d37.8402608!4d-122.2950182!16s%2Fg%2F11g1m85k8x!19sChIJfV5kS1t-hYARBL_LHRqwqYM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Behavioral Health Concepts, Inc.</t>
+  </si>
+  <si>
+    <t>Corporate office</t>
+  </si>
+  <si>
+    <t>5901 Christie Ave</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Trumpet+Behavioral+Health,+a+division+of+BlueSprig/data=!4m7!3m6!1s0x808dff4c55b47263:0xbfb7a3c8e4d16611!8m2!3d36.6877017!4d-121.6719324!16s%2Fg%2F11b6d2wkvg!19sChIJY3K0VUz_jYAREWbR5Mijt78?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Applied behavior analysis therapist</t>
+  </si>
+  <si>
+    <t>4 Rossi Cir Ste 101</t>
+  </si>
+  <si>
     <t>https://www.bluesprigautism.com/centers/california/salinas/?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=gbp</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kings+View+Behavioral+Health+and+IT+Company/data=!4m7!3m6!1s0x809442b2c80742dd:0x294cc3a181383b70!8m2!3d36.8378279!4d-119.8152641!16s%2Fg%2F1td7hztg!19sChIJ3UIHyLJClIARcDs4gaHDTCk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>Kings View Behavioral Health and IT Company</t>
+  </si>
+  <si>
+    <t>1396 W Herndon Ave</t>
   </si>
   <si>
     <t>https://www.kingsview.org/?utm_source=cumulus&amp;utm_medium=onlinepresence&amp;utm_campaign=gbp</t>
@@ -348,7 +1443,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -364,13 +1459,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="2"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -386,12 +1495,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -728,546 +1840,2005 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D465691D-9523-402A-8B2B-D9818D5AA79D}">
-  <dimension ref="A1:A106"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE3FF363-717F-491C-B9F1-9170D6273726}">
+  <dimension ref="A1:E121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="162.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="74.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="162.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="D111" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="D113" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
-        <v>100</v>
+      <c r="D114" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>465</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" xr:uid="{F150B0F2-D31C-4014-8FF4-28061422DC2C}"/>
+    <hyperlink ref="E4" r:id="rId1" xr:uid="{EE30F204-5125-4543-A3FA-C7BB2029902B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
